--- a/branches/feat/sp-inf-feat/StructureDefinition-mii-ex-biobank-modifikationen.xlsx
+++ b/branches/feat/sp-inf-feat/StructureDefinition-mii-ex-biobank-modifikationen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:06:55+00:00</t>
+    <t>2026-09-10T14:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/sp-inf-feat/StructureDefinition-mii-ex-biobank-modifikationen.xlsx
+++ b/branches/feat/sp-inf-feat/StructureDefinition-mii-ex-biobank-modifikationen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:15:53+00:00</t>
+    <t>2026-09-10T14:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
